--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T01:52:46+00:00</t>
+    <t>2024-12-30T05:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T05:25:46+00:00</t>
+    <t>2024-12-30T06:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T06:06:44+00:00</t>
+    <t>2024-12-30T09:02:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:02:09+00:00</t>
+    <t>2024-12-30T09:11:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:11:40+00:00</t>
+    <t>2024-12-30T09:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T09:24:38+00:00</t>
+    <t>2024-12-30T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T10:20:10+00:00</t>
+    <t>2024-12-31T04:42:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-31T04:42:12+00:00</t>
+    <t>2025-01-02T04:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T04:55:17+00:00</t>
+    <t>2025-01-02T05:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T06:27:10+00:00</t>
+    <t>2025-01-02T07:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T01:45:27+00:00</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
